--- a/main/ig/StructureDefinition-as-dp-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-dp-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:10:07+00:00</t>
+    <t>2026-09-22T15:44:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1893,7 +1893,7 @@
     <t>These could be such things as is wheelchair accessible.</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J138-TypeActivite-RASS/FHIR/JDV-J138-TypeActivite-RASS|20240223120000</t>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J138-TypeActivite-RASS/FHIR/JDV-J138-TypeActivite-RASS|20260730120000</t>
   </si>
   <si>
     <t>HealthcareService.communication</t>
